--- a/templates/site-data-template.xlsx
+++ b/templates/site-data-template.xlsx
@@ -433,22 +433,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>この行のように type が # で始まる行は読み込まれません（メモ欄として使えます）</t>
+          <t>type が # で始まる行は読み込まれません（メモ欄として使えます）</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>post＝ブログ記事 / news＝トップのお知らせ（部誌発売中など）/ link＝SNS などのリンク</t>
+          <t>post＝ブログ記事 / news＝トップの販売・お知らせタイル（部誌 PDF、Tシャツなど）/ link＝SNS などのリンク</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>news で TRUE → 全ページ上部の帯にも表示 / post で TRUE → 一覧の先頭に固定</t>
+          <t>news で TRUE → 他のページ上部の帯にも表示 / post で TRUE → 一覧の先頭に固定</t>
         </is>
       </c>
     </row>
@@ -616,103 +616,43 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>画像 URL。Google ドライブの共有リンク（リンクを知っている全員が閲覧可）もそのまま貼れます</t>
+          <t>画像 URL（Google ドライブの共有リンクも可）。news では pdf / tshirt と書くと内蔵イラストを表示</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t># url</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>リンク先。PDF 販売ページや Tシャツの購入フォームの URL を入れる。サイト内なら projects/aorxc.html のように書ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t># style</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>news のタイル色。light（白）/ dark（黒）。空欄なら自動</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Aoristos 部誌、発売中。</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>会場では冊子版、オンラインでは PDF 版を販売しています。</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>https://example.com/bushi</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>PDF 版を購入</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>news</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>SF 2026 公式 T シャツ</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>テーマ「融合」をまとったオリジナルデザイン。数量限定です。</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>https://example.com/tshirt</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>予約する</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>dark</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t># 注意</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>news の行が1つもないときは、サイトに組み込まれた部誌・Tシャツのタイルが表示されます</t>
         </is>
       </c>
     </row>
@@ -723,36 +663,44 @@
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>電気工学部 部誌</t>
+          <t>Aoristos 部誌、PDF 版 発売中。</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>回路と工作の一年をまとめた一冊。物理実験室で販売します。</t>
+          <t>SF 当日は、会場で冊子版も販売します。</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>projects/electric-bushi.html</t>
+          <t>https://example.com/aoristos-pdf</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>詳しく見る</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+          <t>PDF 版を購入</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>light</t>
         </is>
       </c>
     </row>
@@ -768,31 +716,35 @@
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>AorXC、挑戦者募集。</t>
+          <t>Aoristos Tシャツ、発売中。</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>小学生から大人まで。その場で解く、オリジナル問題。</t>
+          <t>サイズ・価格は購入ページでご確認ください。</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>projects/aorxc.html</t>
+          <t>https://example.com/tshirt</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>詳しく見る</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+          <t>購入する</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>tshirt</t>
+        </is>
+      </c>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>dark</t>
         </is>
       </c>
     </row>
@@ -813,7 +765,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>@sf2026_example</t>
+          <t>@aoristos_example</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
@@ -845,7 +797,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>@sf2026_example</t>
+          <t>@aoristos_example</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr"/>
@@ -879,27 +831,30 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>theme-2026</t>
+          <t>sf2026</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>今年のテーマは「融合」です</t>
+          <t>SF 2026 に出展します</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>11月7日（土）・8日（日）の2日間で開催する SF 2026。テーマに込めた思いをお伝えします。</t>
+          <t>11月7日（土）午後・8日（日）、Aoristos は SF 2026 で企画を行います。</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>今年の SF のテーマは **「融合」** に決まりました。
-## テーマに込めたこと
-部活、クラス、学年。ふだんは別々に積み重ねてきたものが、二日間だけ一つの校舎に集まります。
-- 1日目：11月7日（土）
-- 2日目：11月8日（日）
-最新情報は [ブログ一覧](blog.html) と公式 SNS でお知らせします。</t>
+          <t>今年も Aoristos は大阪星光学院の SF に出展します。SF 2026 のテーマは **「融合」** です。
+## 日時
+- 1日目：11月7日（土）午後のみ（15:30 頃まで）
+- 2日目：11月8日（日）9:00 〜 15:30 頃
+## 企画
+- AorXC（オリジナル問題に挑戦）
+- 部誌の販売（冊子版・PDF 版）
+- 「科学の甲子園」展示、実績展示
+時間は [タイムテーブル](timetable.html) をご覧ください。</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
@@ -907,12 +862,12 @@
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>お知らせ,テーマ</t>
+          <t>お知らせ</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>SF 実行委員会</t>
+          <t>Aoristos</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
@@ -932,17 +887,17 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>bushi-on-sale</t>
+          <t>bushi-pdf</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Aoristos 部誌の販売を開始しました</t>
+          <t>部誌の PDF 版を販売します</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>今年の部誌は、オンラインでも PDF 版を購入できます。</t>
+          <t>今年の部誌は、オンラインで PDF 版も購入できます。</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -950,8 +905,7 @@
           <t>部員それぞれのテーマで書き上げた記事をまとめた、Aoristos の部誌が完成しました。
 ## 購入方法
 1. 冊子版：SF 当日、会場で購入
-2. PDF 版：オンラインで購入（リンクはトップページから）
-&gt; 数に限りがあります。お早めにどうぞ。</t>
+2. PDF 版：オンラインで購入（リンクはトップページから）</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
@@ -959,7 +913,7 @@
       <c r="K18" s="3" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>販売,Aoristos</t>
+          <t>販売</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -975,100 +929,53 @@
           <t>post</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>2026/10/05</t>
+          <t>2026/10/01</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>preparing</t>
+          <t>draft-sample</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>準備、進んでいます</t>
+          <t>（下書きの例）この記事は表示されません</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>放課後の校舎で、各企画の準備が本格的に始まりました。</t>
+          <t>visible を FALSE にすると、公開前の下書きとして置いておけます。</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>放課後の校舎のあちこちで、工具の音や練習の声が聞こえるようになりました。
-本番まであと少し。当日の様子もこのブログでお届けします。</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>準備</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>SF 実行委員会</t>
-        </is>
-      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>2026/10/01</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>draft-sample</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>（下書きの例）この記事は表示されません</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>visible を FALSE にすると、公開前の下書きとして置いておけます。</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="B5:N5"/>
     <mergeCell ref="B9:N9"/>
     <mergeCell ref="B8:N8"/>
     <mergeCell ref="B4:N4"/>
+    <mergeCell ref="B12:N12"/>
     <mergeCell ref="B7:N7"/>
+    <mergeCell ref="B11:N11"/>
     <mergeCell ref="B6:N6"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B2:N2"/>
